--- a/app/content/jianfeng.xlsx
+++ b/app/content/jianfeng.xlsx
@@ -974,7 +974,7 @@
         <v>诛心之议</v>
       </c>
       <c r="C2" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D2" t="str">
         <v>不谈他的罪，只谈沙盘、横渠、长河落日。</v>
@@ -997,7 +997,7 @@
         <v>断其四肢</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D3" t="str">
         <v>暗室之中，先断其四肢，再置于殿上。</v>
@@ -1020,7 +1020,7 @@
         <v>攻心为上</v>
       </c>
       <c r="C4" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D4" t="str">
         <v>不必在乎一城一池，攻城为下，攻心为上。</v>
@@ -1043,7 +1043,7 @@
         <v>毁堤开闸</v>
       </c>
       <c r="C5" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D5" t="str">
         <v>借端午汛潮，以水为兵。</v>
@@ -1066,7 +1066,7 @@
         <v>十倍围之</v>
       </c>
       <c r="C6" t="str">
-        <v>理</v>
+        <v>势</v>
       </c>
       <c r="D6" t="str">
         <v>围三阙一，慢慢耗死这座城。</v>
@@ -1089,7 +1089,7 @@
         <v>劝降不屠</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D7" t="str">
         <v>一遍又一遍地派使者：降者，不屠。</v>
